--- a/Data_Ecoli/P1_2.xlsx
+++ b/Data_Ecoli/P1_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Degas_Experiment\Data_Ecoli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Degas_experiment\Data_Ecoli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0AC795-560A-4311-AF0B-1C4B2D306512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6FC735F-87A7-4291-859F-5105FCFC1990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="10">
   <si>
     <t>Group</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,10 +64,6 @@
   </si>
   <si>
     <t>75_unstirred_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>75_unstirred_3</t>
   </si>
 </sst>
 </file>
@@ -396,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -1353,19 +1349,19 @@
         <v>1</v>
       </c>
       <c r="C42">
-        <v>25.556000000000001</v>
+        <v>21.257000000000001</v>
       </c>
       <c r="D42">
-        <v>1.3140000000000001</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="E42">
-        <v>0.27300000000000002</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="F42">
-        <v>280.8</v>
+        <v>688.3</v>
       </c>
       <c r="G42" s="1">
-        <v>101010.45</v>
+        <v>181975.11</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1376,19 +1372,19 @@
         <v>2</v>
       </c>
       <c r="C43">
-        <v>25.12</v>
+        <v>21.227</v>
       </c>
       <c r="D43">
-        <v>0.79300000000000004</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="E43">
-        <v>0.19500000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="F43">
-        <v>322.10000000000002</v>
+        <v>878</v>
       </c>
       <c r="G43" s="1">
-        <v>167584.09</v>
+        <v>277459.31</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1399,19 +1395,19 @@
         <v>3</v>
       </c>
       <c r="C44">
-        <v>25.783000000000001</v>
+        <v>21.082000000000001</v>
       </c>
       <c r="D44">
-        <v>0.751</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="E44">
-        <v>0.24199999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="F44">
-        <v>233.8</v>
+        <v>1035</v>
       </c>
       <c r="G44" s="1">
-        <v>146984.71</v>
+        <v>264156.92</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1422,19 +1418,19 @@
         <v>4</v>
       </c>
       <c r="C45">
-        <v>25.844999999999999</v>
+        <v>20.991</v>
       </c>
       <c r="D45">
-        <v>1.0649999999999999</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="E45">
-        <v>0.20100000000000001</v>
+        <v>0.255</v>
       </c>
       <c r="F45">
-        <v>92.7</v>
+        <v>1281.0999999999999</v>
       </c>
       <c r="G45" s="1">
-        <v>77655.66</v>
+        <v>364156.53</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1445,19 +1441,19 @@
         <v>5</v>
       </c>
       <c r="C46">
-        <v>25.934000000000001</v>
+        <v>21.106999999999999</v>
       </c>
       <c r="D46">
-        <v>0.745</v>
+        <v>0.499</v>
       </c>
       <c r="E46">
-        <v>0.224</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="F46">
-        <v>165.1</v>
+        <v>1322.6</v>
       </c>
       <c r="G46" s="1">
-        <v>241316.21</v>
+        <v>343219.14</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1468,19 +1464,19 @@
         <v>6</v>
       </c>
       <c r="C47">
-        <v>28.783999999999999</v>
+        <v>20.829000000000001</v>
       </c>
       <c r="D47">
-        <v>0.84799999999999998</v>
+        <v>0.499</v>
       </c>
       <c r="E47">
-        <v>0.214</v>
+        <v>0.154</v>
       </c>
       <c r="F47">
-        <v>204.8</v>
+        <v>848.9</v>
       </c>
       <c r="G47" s="1">
-        <v>135029.74</v>
+        <v>312391.56</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1491,19 +1487,19 @@
         <v>7</v>
       </c>
       <c r="C48">
-        <v>25.873000000000001</v>
+        <v>21.166</v>
       </c>
       <c r="D48">
-        <v>0.84799999999999998</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="E48">
-        <v>0.224</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="F48">
-        <v>115.1</v>
+        <v>1825.5</v>
       </c>
       <c r="G48" s="1">
-        <v>235256.07</v>
+        <v>474932.82</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1514,19 +1510,19 @@
         <v>8</v>
       </c>
       <c r="C49">
-        <v>26.998999999999999</v>
+        <v>21.128</v>
       </c>
       <c r="D49">
-        <v>0.59599999999999997</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="E49">
-        <v>0.188</v>
+        <v>9.4E-2</v>
       </c>
       <c r="F49">
-        <v>74.900000000000006</v>
+        <v>1514.2</v>
       </c>
       <c r="G49" s="1">
-        <v>109454.94</v>
+        <v>469677.69</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1537,19 +1533,19 @@
         <v>9</v>
       </c>
       <c r="C50">
-        <v>26.402999999999999</v>
+        <v>21.100999999999999</v>
       </c>
       <c r="D50">
-        <v>0.748</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="E50">
-        <v>0.20300000000000001</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="F50">
-        <v>133.80000000000001</v>
+        <v>1672.2</v>
       </c>
       <c r="G50" s="1">
-        <v>212042.34</v>
+        <v>467247.99</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1560,19 +1556,19 @@
         <v>10</v>
       </c>
       <c r="C51">
-        <v>26.456</v>
+        <v>21.111999999999998</v>
       </c>
       <c r="D51">
-        <v>0.59499999999999997</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="E51">
-        <v>0.22700000000000001</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="F51">
-        <v>336.6</v>
+        <v>1148.5999999999999</v>
       </c>
       <c r="G51" s="1">
-        <v>204469.41</v>
+        <v>245253.87</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1583,19 +1579,19 @@
         <v>11</v>
       </c>
       <c r="C52">
-        <v>27.952999999999999</v>
+        <v>21.15</v>
       </c>
       <c r="D52">
-        <v>0.78200000000000003</v>
+        <v>0.505</v>
       </c>
       <c r="E52">
-        <v>0.22</v>
+        <v>0.224</v>
       </c>
       <c r="F52">
-        <v>266.89999999999998</v>
+        <v>846.1</v>
       </c>
       <c r="G52" s="1">
-        <v>158986.57</v>
+        <v>456701.75</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -1606,19 +1602,19 @@
         <v>12</v>
       </c>
       <c r="C53">
-        <v>28.143000000000001</v>
+        <v>21.045000000000002</v>
       </c>
       <c r="D53">
-        <v>0.76500000000000001</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="E53">
-        <v>0.25600000000000001</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="F53">
-        <v>332.1</v>
+        <v>1459.8</v>
       </c>
       <c r="G53" s="1">
-        <v>223670.48</v>
+        <v>452606.39</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -1629,19 +1625,19 @@
         <v>13</v>
       </c>
       <c r="C54">
-        <v>29.297999999999998</v>
+        <v>20.998999999999999</v>
       </c>
       <c r="D54">
         <v>0.64900000000000002</v>
       </c>
       <c r="E54">
-        <v>0.2</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="F54">
-        <v>232.3</v>
+        <v>1299.5999999999999</v>
       </c>
       <c r="G54" s="1">
-        <v>122258.84</v>
+        <v>439329.93</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -1652,19 +1648,19 @@
         <v>14</v>
       </c>
       <c r="C55">
-        <v>28.297000000000001</v>
+        <v>21.065000000000001</v>
       </c>
       <c r="D55">
-        <v>0.71199999999999997</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="E55">
-        <v>0.20300000000000001</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="F55">
-        <v>213.2</v>
+        <v>952.6</v>
       </c>
       <c r="G55" s="1">
-        <v>121538.94</v>
+        <v>401869.37</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -1675,19 +1671,19 @@
         <v>15</v>
       </c>
       <c r="C56">
-        <v>29.983000000000001</v>
+        <v>21.366</v>
       </c>
       <c r="D56">
-        <v>0.81499999999999995</v>
+        <v>0.54600000000000004</v>
       </c>
       <c r="E56">
-        <v>0.25700000000000001</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="F56">
-        <v>449.2</v>
+        <v>1587.2</v>
       </c>
       <c r="G56" s="1">
-        <v>242826.52</v>
+        <v>387965.27</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -1698,19 +1694,19 @@
         <v>16</v>
       </c>
       <c r="C57">
-        <v>30.210999999999999</v>
+        <v>21.364999999999998</v>
       </c>
       <c r="D57">
-        <v>0.91500000000000004</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="E57">
-        <v>0.24</v>
+        <v>0.185</v>
       </c>
       <c r="F57">
-        <v>311.10000000000002</v>
+        <v>1385.3</v>
       </c>
       <c r="G57" s="1">
-        <v>157510.04</v>
+        <v>39511.279999999999</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -1721,19 +1717,19 @@
         <v>17</v>
       </c>
       <c r="C58">
-        <v>30.114999999999998</v>
+        <v>21.763999999999999</v>
       </c>
       <c r="D58">
-        <v>1.131</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="E58">
-        <v>0.221</v>
+        <v>9.0999999999999998E-2</v>
       </c>
       <c r="F58">
-        <v>120.8</v>
+        <v>1835.8</v>
       </c>
       <c r="G58" s="1">
-        <v>97374.54</v>
+        <v>468166.2</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -1744,19 +1740,19 @@
         <v>18</v>
       </c>
       <c r="C59">
-        <v>31.42</v>
+        <v>21.841999999999999</v>
       </c>
       <c r="D59">
-        <v>1.1639999999999999</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="E59">
-        <v>0.20699999999999999</v>
+        <v>0.222</v>
       </c>
       <c r="F59">
-        <v>203.8</v>
+        <v>1692.6</v>
       </c>
       <c r="G59" s="1">
-        <v>68842</v>
+        <v>470581.77</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -1767,19 +1763,19 @@
         <v>19</v>
       </c>
       <c r="C60">
-        <v>31.571999999999999</v>
+        <v>22.001000000000001</v>
       </c>
       <c r="D60">
-        <v>1.1140000000000001</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="E60">
-        <v>0.22</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="F60">
-        <v>156.9</v>
+        <v>988.6</v>
       </c>
       <c r="G60" s="1">
-        <v>70131.820000000007</v>
+        <v>319670.8</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -1790,478 +1786,18 @@
         <v>20</v>
       </c>
       <c r="C61">
-        <v>33.109000000000002</v>
+        <v>22.056999999999999</v>
       </c>
       <c r="D61">
-        <v>1.3640000000000001</v>
+        <v>0.748</v>
       </c>
       <c r="E61">
-        <v>0.27800000000000002</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="F61">
-        <v>169.8</v>
+        <v>1016.2</v>
       </c>
       <c r="G61" s="1">
-        <v>70659</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62">
-        <v>21.257000000000001</v>
-      </c>
-      <c r="D62">
-        <v>0.48199999999999998</v>
-      </c>
-      <c r="E62">
-        <v>0.16200000000000001</v>
-      </c>
-      <c r="F62">
-        <v>688.3</v>
-      </c>
-      <c r="G62" s="1">
-        <v>181975.11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>10</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63">
-        <v>21.227</v>
-      </c>
-      <c r="D63">
-        <v>0.34899999999999998</v>
-      </c>
-      <c r="E63">
-        <v>0.16</v>
-      </c>
-      <c r="F63">
-        <v>878</v>
-      </c>
-      <c r="G63" s="1">
-        <v>277459.31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
-      </c>
-      <c r="C64">
-        <v>21.082000000000001</v>
-      </c>
-      <c r="D64">
-        <v>0.83199999999999996</v>
-      </c>
-      <c r="E64">
-        <v>0.16</v>
-      </c>
-      <c r="F64">
-        <v>1035</v>
-      </c>
-      <c r="G64" s="1">
-        <v>264156.92</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>10</v>
-      </c>
-      <c r="B65">
-        <v>4</v>
-      </c>
-      <c r="C65">
-        <v>20.991</v>
-      </c>
-      <c r="D65">
-        <v>0.66300000000000003</v>
-      </c>
-      <c r="E65">
-        <v>0.255</v>
-      </c>
-      <c r="F65">
-        <v>1281.0999999999999</v>
-      </c>
-      <c r="G65" s="1">
-        <v>364156.53</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>10</v>
-      </c>
-      <c r="B66">
-        <v>5</v>
-      </c>
-      <c r="C66">
-        <v>21.106999999999999</v>
-      </c>
-      <c r="D66">
-        <v>0.499</v>
-      </c>
-      <c r="E66">
-        <v>7.0999999999999994E-2</v>
-      </c>
-      <c r="F66">
-        <v>1322.6</v>
-      </c>
-      <c r="G66" s="1">
-        <v>343219.14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>10</v>
-      </c>
-      <c r="B67">
-        <v>6</v>
-      </c>
-      <c r="C67">
-        <v>20.829000000000001</v>
-      </c>
-      <c r="D67">
-        <v>0.499</v>
-      </c>
-      <c r="E67">
-        <v>0.154</v>
-      </c>
-      <c r="F67">
-        <v>848.9</v>
-      </c>
-      <c r="G67" s="1">
-        <v>312391.56</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>10</v>
-      </c>
-      <c r="B68">
-        <v>7</v>
-      </c>
-      <c r="C68">
-        <v>21.166</v>
-      </c>
-      <c r="D68">
-        <v>0.54900000000000004</v>
-      </c>
-      <c r="E68">
-        <v>7.9000000000000001E-2</v>
-      </c>
-      <c r="F68">
-        <v>1825.5</v>
-      </c>
-      <c r="G68" s="1">
-        <v>474932.82</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>10</v>
-      </c>
-      <c r="B69">
-        <v>8</v>
-      </c>
-      <c r="C69">
-        <v>21.128</v>
-      </c>
-      <c r="D69">
-        <v>0.56599999999999995</v>
-      </c>
-      <c r="E69">
-        <v>9.4E-2</v>
-      </c>
-      <c r="F69">
-        <v>1514.2</v>
-      </c>
-      <c r="G69" s="1">
-        <v>469677.69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>10</v>
-      </c>
-      <c r="B70">
-        <v>9</v>
-      </c>
-      <c r="C70">
-        <v>21.100999999999999</v>
-      </c>
-      <c r="D70">
-        <v>0.63200000000000001</v>
-      </c>
-      <c r="E70">
-        <v>0.17899999999999999</v>
-      </c>
-      <c r="F70">
-        <v>1672.2</v>
-      </c>
-      <c r="G70" s="1">
-        <v>467247.99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>10</v>
-      </c>
-      <c r="B71">
-        <v>10</v>
-      </c>
-      <c r="C71">
-        <v>21.111999999999998</v>
-      </c>
-      <c r="D71">
-        <v>0.51600000000000001</v>
-      </c>
-      <c r="E71">
-        <v>0.16600000000000001</v>
-      </c>
-      <c r="F71">
-        <v>1148.5999999999999</v>
-      </c>
-      <c r="G71" s="1">
-        <v>245253.87</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>10</v>
-      </c>
-      <c r="B72">
-        <v>11</v>
-      </c>
-      <c r="C72">
-        <v>21.15</v>
-      </c>
-      <c r="D72">
-        <v>0.505</v>
-      </c>
-      <c r="E72">
-        <v>0.224</v>
-      </c>
-      <c r="F72">
-        <v>846.1</v>
-      </c>
-      <c r="G72" s="1">
-        <v>456701.75</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>10</v>
-      </c>
-      <c r="B73">
-        <v>12</v>
-      </c>
-      <c r="C73">
-        <v>21.045000000000002</v>
-      </c>
-      <c r="D73">
-        <v>0.81499999999999995</v>
-      </c>
-      <c r="E73">
-        <v>0.23100000000000001</v>
-      </c>
-      <c r="F73">
-        <v>1459.8</v>
-      </c>
-      <c r="G73" s="1">
-        <v>452606.39</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>10</v>
-      </c>
-      <c r="B74">
-        <v>13</v>
-      </c>
-      <c r="C74">
-        <v>20.998999999999999</v>
-      </c>
-      <c r="D74">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="E74">
-        <v>0.17699999999999999</v>
-      </c>
-      <c r="F74">
-        <v>1299.5999999999999</v>
-      </c>
-      <c r="G74" s="1">
-        <v>439329.93</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>10</v>
-      </c>
-      <c r="B75">
-        <v>14</v>
-      </c>
-      <c r="C75">
-        <v>21.065000000000001</v>
-      </c>
-      <c r="D75">
-        <v>0.48199999999999998</v>
-      </c>
-      <c r="E75">
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="F75">
-        <v>952.6</v>
-      </c>
-      <c r="G75" s="1">
-        <v>401869.37</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>10</v>
-      </c>
-      <c r="B76">
-        <v>15</v>
-      </c>
-      <c r="C76">
-        <v>21.366</v>
-      </c>
-      <c r="D76">
-        <v>0.54600000000000004</v>
-      </c>
-      <c r="E76">
-        <v>0.30399999999999999</v>
-      </c>
-      <c r="F76">
-        <v>1587.2</v>
-      </c>
-      <c r="G76" s="1">
-        <v>387965.27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77">
-        <v>16</v>
-      </c>
-      <c r="C77">
-        <v>21.364999999999998</v>
-      </c>
-      <c r="D77">
-        <v>0.61499999999999999</v>
-      </c>
-      <c r="E77">
-        <v>0.185</v>
-      </c>
-      <c r="F77">
-        <v>1385.3</v>
-      </c>
-      <c r="G77" s="1">
-        <v>39511.279999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>10</v>
-      </c>
-      <c r="B78">
-        <v>17</v>
-      </c>
-      <c r="C78">
-        <v>21.763999999999999</v>
-      </c>
-      <c r="D78">
-        <v>0.51600000000000001</v>
-      </c>
-      <c r="E78">
-        <v>9.0999999999999998E-2</v>
-      </c>
-      <c r="F78">
-        <v>1835.8</v>
-      </c>
-      <c r="G78" s="1">
-        <v>468166.2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>10</v>
-      </c>
-      <c r="B79">
-        <v>18</v>
-      </c>
-      <c r="C79">
-        <v>21.841999999999999</v>
-      </c>
-      <c r="D79">
-        <v>0.74199999999999999</v>
-      </c>
-      <c r="E79">
-        <v>0.222</v>
-      </c>
-      <c r="F79">
-        <v>1692.6</v>
-      </c>
-      <c r="G79" s="1">
-        <v>470581.77</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>10</v>
-      </c>
-      <c r="B80">
-        <v>19</v>
-      </c>
-      <c r="C80">
-        <v>22.001000000000001</v>
-      </c>
-      <c r="D80">
-        <v>0.84799999999999998</v>
-      </c>
-      <c r="E80">
-        <v>0.22900000000000001</v>
-      </c>
-      <c r="F80">
-        <v>988.6</v>
-      </c>
-      <c r="G80" s="1">
-        <v>319670.8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>10</v>
-      </c>
-      <c r="B81">
-        <v>20</v>
-      </c>
-      <c r="C81">
-        <v>22.056999999999999</v>
-      </c>
-      <c r="D81">
-        <v>0.748</v>
-      </c>
-      <c r="E81">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="F81">
-        <v>1016.2</v>
-      </c>
-      <c r="G81" s="1">
         <v>328623.62</v>
       </c>
     </row>
